--- a/daftar tanggal kosong (edit).xlsx
+++ b/daftar tanggal kosong (edit).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester7\PraTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{DC0E1DD8-9A04-4760-B415-E9783AAFEB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4F5DB41E-0AC0-4545-93EF-9C88CC6C0D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{9CDB38A4-16EB-4777-97BE-9A553C136956}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{9CDB38A4-16EB-4777-97BE-9A553C136956}"/>
   </bookViews>
   <sheets>
     <sheet name="daftar_tanggal_kosong" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,16 +282,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -661,15 +656,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1073,7 +1068,7 @@
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1084,7 +1079,7 @@
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1095,7 +1090,7 @@
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1161,10 +1156,10 @@
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
@@ -1173,7 +1168,7 @@
       <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1184,7 +1179,7 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1195,7 +1190,7 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
@@ -1204,7 +1199,7 @@
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
@@ -1213,7 +1208,7 @@
       <c r="B15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="8"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
@@ -1222,7 +1217,7 @@
       <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
@@ -1396,7 +1391,7 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1407,7 +1402,7 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
@@ -1416,7 +1411,7 @@
       <c r="B34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="10"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
@@ -1425,7 +1420,7 @@
       <c r="B35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
@@ -1434,7 +1429,7 @@
       <c r="B36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="8"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
@@ -1586,7 +1581,7 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1597,7 +1592,7 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
@@ -1606,7 +1601,7 @@
       <c r="B52" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="10"/>
+      <c r="C52" s="8"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
@@ -1615,7 +1610,7 @@
       <c r="B53" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
@@ -1624,7 +1619,7 @@
       <c r="B54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="10"/>
+      <c r="C54" s="8"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
@@ -1633,7 +1628,7 @@
       <c r="B55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="8"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
@@ -1642,7 +1637,7 @@
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="10"/>
+      <c r="C56" s="8"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
@@ -1695,7 +1690,7 @@
       <c r="B61" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1706,7 +1701,7 @@
       <c r="B62" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C62" s="10"/>
+      <c r="C62" s="8"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
@@ -1715,7 +1710,7 @@
       <c r="B63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1726,7 +1721,7 @@
       <c r="B64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="10"/>
+      <c r="C64" s="8"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
